--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>22.09809973074246</v>
+      </c>
+      <c r="C2">
         <v>29.54029372271394</v>
-      </c>
-      <c r="C2">
-        <v>22.09809973074246</v>
       </c>
       <c r="D2">
         <v>3.385206692210667</v>
       </c>
       <c r="E2">
-        <v>19.48074827881963</v>
+        <v>14.57289227844873</v>
       </c>
       <c r="F2">
         <v>65.94635944273163</v>
       </c>
       <c r="G2">
-        <v>14.57289227844873</v>
+        <v>19.48074827881963</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.98110215409013</v>
+      </c>
+      <c r="C3">
         <v>25.0786308973173</v>
-      </c>
-      <c r="C3">
-        <v>28.98110215409013</v>
       </c>
       <c r="D3">
         <v>3.987458502397639</v>
       </c>
       <c r="E3">
+        <v>18.81160091613268</v>
+      </c>
+      <c r="F3">
+        <v>64.90988788526037</v>
+      </c>
+      <c r="G3">
         <v>16.27851119860693</v>
-      </c>
-      <c r="F3">
-        <v>64.90988788526039</v>
-      </c>
-      <c r="G3">
-        <v>18.81160091613268</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.97049083690206</v>
+      </c>
+      <c r="C4">
         <v>28.03197114967838</v>
-      </c>
-      <c r="C4">
-        <v>25.97049083690206</v>
       </c>
       <c r="D4">
         <v>3.567355269668481</v>
       </c>
       <c r="E4">
-        <v>18.2022876699991</v>
+        <v>16.863685490408</v>
       </c>
       <c r="F4">
         <v>64.9340268395929</v>
       </c>
       <c r="G4">
-        <v>16.863685490408</v>
+        <v>18.2022876699991</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.58045160271593</v>
+      </c>
+      <c r="C5">
         <v>41.67061424285489</v>
-      </c>
-      <c r="C5">
-        <v>28.58045160271593</v>
       </c>
       <c r="D5">
         <v>2.399772641151952</v>
       </c>
       <c r="E5">
-        <v>24.47597848265628</v>
+        <v>16.78723798924133</v>
       </c>
       <c r="F5">
         <v>58.73678352810239</v>
       </c>
       <c r="G5">
-        <v>16.78723798924133</v>
+        <v>24.47597848265628</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.87064518183556</v>
+      </c>
+      <c r="C6">
         <v>26.62250812050188</v>
-      </c>
-      <c r="C6">
-        <v>30.87064518183556</v>
       </c>
       <c r="D6">
         <v>3.75622009569378</v>
       </c>
       <c r="E6">
+        <v>19.60126172759625</v>
+      </c>
+      <c r="F6">
+        <v>63.49482368165641</v>
+      </c>
+      <c r="G6">
         <v>16.90391459074733</v>
-      </c>
-      <c r="F6">
-        <v>63.49482368165643</v>
-      </c>
-      <c r="G6">
-        <v>19.60126172759625</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.22260049757758</v>
+      </c>
+      <c r="C7">
         <v>31.45214089302082</v>
-      </c>
-      <c r="C7">
-        <v>25.22260049757758</v>
       </c>
       <c r="D7">
         <v>3.179433805162365</v>
       </c>
       <c r="E7">
-        <v>20.07479994149725</v>
+        <v>16.09870249263492</v>
       </c>
       <c r="F7">
         <v>63.82649756586783</v>
       </c>
       <c r="G7">
-        <v>16.09870249263492</v>
+        <v>20.07479994149725</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.01740566637022</v>
+      </c>
+      <c r="C8">
         <v>30.03112692161098</v>
-      </c>
-      <c r="C8">
-        <v>28.01740566637022</v>
       </c>
       <c r="D8">
         <v>3.329878371232152</v>
       </c>
       <c r="E8">
-        <v>19.00120578778135</v>
+        <v>17.72709003215434</v>
       </c>
       <c r="F8">
         <v>63.2717041800643</v>
       </c>
       <c r="G8">
-        <v>17.72709003215434</v>
+        <v>19.00120578778135</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.59315497710292</v>
+      </c>
+      <c r="C9">
         <v>21.83176669076886</v>
-      </c>
-      <c r="C9">
-        <v>31.59315497710292</v>
       </c>
       <c r="D9">
         <v>4.580481342459704</v>
       </c>
       <c r="E9">
-        <v>14.22960914917683</v>
+        <v>20.59193163252482</v>
       </c>
       <c r="F9">
         <v>65.17845921829834</v>
       </c>
       <c r="G9">
-        <v>20.59193163252482</v>
+        <v>14.22960914917683</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.27597061909758</v>
+      </c>
+      <c r="C10">
         <v>32.7177334732424</v>
-      </c>
-      <c r="C10">
-        <v>29.27597061909758</v>
       </c>
       <c r="D10">
         <v>3.056446440025657</v>
       </c>
       <c r="E10">
-        <v>20.19691669905428</v>
+        <v>18.0722891566265</v>
       </c>
       <c r="F10">
         <v>61.73079414431921</v>
       </c>
       <c r="G10">
-        <v>18.0722891566265</v>
+        <v>20.19691669905428</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.41098346642203</v>
+      </c>
+      <c r="C11">
         <v>31.13545858265747</v>
-      </c>
-      <c r="C11">
-        <v>26.41098346642203</v>
       </c>
       <c r="D11">
         <v>3.211772190042522</v>
       </c>
       <c r="E11">
-        <v>19.76271769625748</v>
+        <v>16.76393520724154</v>
       </c>
       <c r="F11">
         <v>63.47334709650098</v>
       </c>
       <c r="G11">
-        <v>16.76393520724154</v>
+        <v>19.76271769625748</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>26.91816401260325</v>
+      </c>
+      <c r="C12">
         <v>33.83292174061143</v>
-      </c>
-      <c r="C12">
-        <v>26.91816401260325</v>
       </c>
       <c r="D12">
         <v>2.955700981625975</v>
       </c>
       <c r="E12">
-        <v>21.04677650050326</v>
+        <v>16.74524553689675</v>
       </c>
       <c r="F12">
         <v>62.20797796259999</v>
       </c>
       <c r="G12">
-        <v>16.74524553689675</v>
+        <v>21.04677650050326</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.35769974012128</v>
+      </c>
+      <c r="C13">
         <v>28.97647764376624</v>
-      </c>
-      <c r="C13">
-        <v>26.35769974012128</v>
       </c>
       <c r="D13">
         <v>3.451075083362079</v>
       </c>
       <c r="E13">
+        <v>16.96838402470936</v>
+      </c>
+      <c r="F13">
+        <v>64.37733258976449</v>
+      </c>
+      <c r="G13">
         <v>18.65428338552615</v>
-      </c>
-      <c r="F13">
-        <v>64.37733258976451</v>
-      </c>
-      <c r="G13">
-        <v>16.96838402470937</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>31.0121906169191</v>
+      </c>
+      <c r="C14">
         <v>28.28469400320158</v>
-      </c>
-      <c r="C14">
-        <v>31.0121906169191</v>
       </c>
       <c r="D14">
         <v>3.535481062255115</v>
       </c>
       <c r="E14">
-        <v>17.7559618134735</v>
+        <v>19.46817145286592</v>
       </c>
       <c r="F14">
         <v>62.77586673366058</v>
       </c>
       <c r="G14">
-        <v>19.46817145286592</v>
+        <v>17.7559618134735</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.32631578947368</v>
+      </c>
+      <c r="C15">
         <v>26.25684210526316</v>
-      </c>
-      <c r="C15">
-        <v>29.32631578947368</v>
       </c>
       <c r="D15">
         <v>3.808531109685696</v>
       </c>
       <c r="E15">
-        <v>16.87640388622771</v>
+        <v>18.84928689345349</v>
       </c>
       <c r="F15">
         <v>64.2743092203188</v>
       </c>
       <c r="G15">
-        <v>18.84928689345349</v>
+        <v>16.87640388622771</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>35.29120443740095</v>
+      </c>
+      <c r="C16">
         <v>29.72464342313788</v>
-      </c>
-      <c r="C16">
-        <v>35.29120443740095</v>
       </c>
       <c r="D16">
         <v>3.364211929356881</v>
       </c>
       <c r="E16">
-        <v>18.01320528211285</v>
+        <v>21.38655462184874</v>
       </c>
       <c r="F16">
         <v>60.60024009603841</v>
       </c>
       <c r="G16">
-        <v>21.38655462184874</v>
+        <v>18.01320528211285</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.20380854348945</v>
+      </c>
+      <c r="C17">
         <v>32.75862068965517</v>
-      </c>
-      <c r="C17">
-        <v>28.20380854348945</v>
       </c>
       <c r="D17">
         <v>3.052631578947369</v>
       </c>
       <c r="E17">
-        <v>20.35171862509992</v>
+        <v>17.52198241406875</v>
       </c>
       <c r="F17">
         <v>62.12629896083133</v>
       </c>
       <c r="G17">
-        <v>17.52198241406875</v>
+        <v>20.35171862509992</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.94967694967695</v>
+      </c>
+      <c r="C18">
         <v>28.33287833287833</v>
-      </c>
-      <c r="C18">
-        <v>26.94967694967695</v>
       </c>
       <c r="D18">
         <v>3.529468443873454</v>
       </c>
       <c r="E18">
-        <v>18.24601500234412</v>
+        <v>17.35525082044069</v>
       </c>
       <c r="F18">
         <v>64.39873417721519</v>
       </c>
       <c r="G18">
-        <v>17.35525082044069</v>
+        <v>18.24601500234412</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>33.08140790326063</v>
+      </c>
+      <c r="C19">
         <v>24.95501331605845</v>
-      </c>
-      <c r="C19">
-        <v>33.08140790326063</v>
       </c>
       <c r="D19">
         <v>4.007210845111047</v>
       </c>
       <c r="E19">
-        <v>15.79067225359811</v>
+        <v>20.93277464018947</v>
       </c>
       <c r="F19">
         <v>63.27655310621242</v>
       </c>
       <c r="G19">
-        <v>20.93277464018947</v>
+        <v>15.79067225359811</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>37.38759335467154</v>
+      </c>
+      <c r="C20">
         <v>24.21886907483615</v>
-      </c>
-      <c r="C20">
-        <v>37.38759335467154</v>
       </c>
       <c r="D20">
         <v>4.12901195720579</v>
       </c>
       <c r="E20">
-        <v>14.9863246251061</v>
+        <v>23.13496180326323</v>
       </c>
       <c r="F20">
         <v>61.87871357163067</v>
       </c>
       <c r="G20">
-        <v>23.13496180326323</v>
+        <v>14.9863246251061</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.08337808906513</v>
+      </c>
+      <c r="C21">
         <v>25.08994062814976</v>
-      </c>
-      <c r="C21">
-        <v>29.08337808906513</v>
       </c>
       <c r="D21">
         <v>3.985661085534997</v>
       </c>
       <c r="E21">
+        <v>18.86407994006404</v>
+      </c>
+      <c r="F21">
+        <v>64.86206616815474</v>
+      </c>
+      <c r="G21">
         <v>16.27385389178123</v>
-      </c>
-      <c r="F21">
-        <v>64.86206616815473</v>
-      </c>
-      <c r="G21">
-        <v>18.86407994006404</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>29.37984496124031</v>
+      </c>
+      <c r="C22">
         <v>37.51937984496124</v>
-      </c>
-      <c r="C22">
-        <v>29.37984496124031</v>
       </c>
       <c r="D22">
         <v>2.665289256198347</v>
       </c>
       <c r="E22">
-        <v>22.480260102183</v>
+        <v>17.60334417092429</v>
       </c>
       <c r="F22">
         <v>59.91639572689271</v>
       </c>
       <c r="G22">
-        <v>17.60334417092429</v>
+        <v>22.480260102183</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.29178383352932</v>
+      </c>
+      <c r="C23">
         <v>27.20998006033028</v>
-      </c>
-      <c r="C23">
-        <v>27.29178383352932</v>
       </c>
       <c r="D23">
         <v>3.675122134535889</v>
       </c>
       <c r="E23">
-        <v>17.61143651345181</v>
+        <v>17.66438333498792</v>
       </c>
       <c r="F23">
         <v>64.72418015156028</v>
       </c>
       <c r="G23">
-        <v>17.66438333498792</v>
+        <v>17.6114365134518</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.58100485373213</v>
+      </c>
+      <c r="C24">
         <v>31.30657221566312</v>
-      </c>
-      <c r="C24">
-        <v>27.58100485373213</v>
       </c>
       <c r="D24">
         <v>3.194217473287241</v>
       </c>
       <c r="E24">
-        <v>19.70359973579921</v>
+        <v>17.35881770145311</v>
       </c>
       <c r="F24">
         <v>62.93758256274769</v>
       </c>
       <c r="G24">
-        <v>17.35881770145311</v>
+        <v>19.70359973579921</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.73761148345559</v>
+      </c>
+      <c r="C25">
         <v>31.32619135574436</v>
-      </c>
-      <c r="C25">
-        <v>27.73761148345559</v>
       </c>
       <c r="D25">
         <v>3.192216981132075</v>
       </c>
       <c r="E25">
-        <v>19.694104376099</v>
+        <v>17.43804120633025</v>
       </c>
       <c r="F25">
         <v>62.86785441757075</v>
       </c>
       <c r="G25">
-        <v>17.43804120633025</v>
+        <v>19.694104376099</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.72409004108559</v>
+      </c>
+      <c r="C26">
         <v>28.75990972744632</v>
-      </c>
-      <c r="C26">
-        <v>27.72409004108559</v>
       </c>
       <c r="D26">
         <v>3.477062374245473</v>
       </c>
       <c r="E26">
-        <v>18.37881813475335</v>
+        <v>17.71688484579543</v>
       </c>
       <c r="F26">
         <v>63.90429701945123</v>
       </c>
       <c r="G26">
-        <v>17.71688484579543</v>
+        <v>18.37881813475335</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.93668425437378</v>
+      </c>
+      <c r="C27">
         <v>28.67259094695918</v>
-      </c>
-      <c r="C27">
-        <v>27.93668425437378</v>
       </c>
       <c r="D27">
         <v>3.487651331719128</v>
       </c>
       <c r="E27">
-        <v>18.30836067027219</v>
+        <v>17.83846085645891</v>
       </c>
       <c r="F27">
         <v>63.8531784732689</v>
       </c>
       <c r="G27">
-        <v>17.83846085645891</v>
+        <v>18.30836067027219</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.99467613132209</v>
+      </c>
+      <c r="C28">
         <v>48.7133984028394</v>
-      </c>
-      <c r="C28">
-        <v>27.99467613132209</v>
       </c>
       <c r="D28">
         <v>2.052823315118397</v>
       </c>
       <c r="E28">
-        <v>27.5671604318353</v>
+        <v>15.84232990208386</v>
       </c>
       <c r="F28">
         <v>56.59050966608085</v>
       </c>
       <c r="G28">
-        <v>15.84232990208386</v>
+        <v>27.5671604318353</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.01675591639316</v>
+      </c>
+      <c r="C29">
         <v>38.74589739160476</v>
-      </c>
-      <c r="C29">
-        <v>27.01675591639316</v>
       </c>
       <c r="D29">
         <v>2.580918412839947</v>
       </c>
       <c r="E29">
-        <v>23.37432263443101</v>
+        <v>16.29845769070446</v>
       </c>
       <c r="F29">
         <v>60.32721967486454</v>
       </c>
       <c r="G29">
-        <v>16.29845769070446</v>
+        <v>23.37432263443101</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.43928419258628</v>
+      </c>
+      <c r="C30">
         <v>37.70771197273115</v>
-      </c>
-      <c r="C30">
-        <v>27.43928419258628</v>
       </c>
       <c r="D30">
         <v>2.651977401129944</v>
       </c>
       <c r="E30">
-        <v>22.8328173374613</v>
+        <v>16.61506707946337</v>
       </c>
       <c r="F30">
         <v>60.55211558307533</v>
       </c>
       <c r="G30">
-        <v>16.61506707946337</v>
+        <v>22.8328173374613</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>30.11864591270273</v>
+      </c>
+      <c r="C31">
         <v>31.99085664525961</v>
-      </c>
-      <c r="C31">
-        <v>30.11864591270273</v>
       </c>
       <c r="D31">
         <v>3.125893160939095</v>
       </c>
       <c r="E31">
-        <v>19.73410326999262</v>
+        <v>18.57919828107164</v>
       </c>
       <c r="F31">
         <v>61.68669844893574</v>
       </c>
       <c r="G31">
-        <v>18.57919828107164</v>
+        <v>19.73410326999262</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>28.5428300495206</v>
+      </c>
+      <c r="C32">
         <v>34.32725740174902</v>
-      </c>
-      <c r="C32">
-        <v>28.5428300495206</v>
       </c>
       <c r="D32">
         <v>2.913136893799877</v>
       </c>
       <c r="E32">
-        <v>21.07646526070643</v>
+        <v>17.52490619743822</v>
       </c>
       <c r="F32">
         <v>61.39862854185535</v>
       </c>
       <c r="G32">
-        <v>17.52490619743822</v>
+        <v>21.07646526070643</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>26.82465172622653</v>
+      </c>
+      <c r="C33">
         <v>39.52150211992731</v>
-      </c>
-      <c r="C33">
-        <v>26.82465172622653</v>
       </c>
       <c r="D33">
         <v>2.530268199233717</v>
       </c>
       <c r="E33">
-        <v>23.7585908697829</v>
+        <v>16.12580219380092</v>
       </c>
       <c r="F33">
         <v>60.11560693641619</v>
       </c>
       <c r="G33">
-        <v>16.12580219380092</v>
+        <v>23.7585908697829</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>42.7468018344195</v>
+      </c>
+      <c r="C34">
         <v>20.2993000241371</v>
-      </c>
-      <c r="C34">
-        <v>42.7468018344195</v>
       </c>
       <c r="D34">
         <v>4.92627824019025</v>
       </c>
       <c r="E34">
-        <v>12.4500370096225</v>
+        <v>26.21761658031088</v>
       </c>
       <c r="F34">
         <v>61.33234641006662</v>
       </c>
       <c r="G34">
-        <v>26.21761658031088</v>
+        <v>12.4500370096225</v>
       </c>
     </row>
   </sheetData>
